--- a/processed_ruby_restored_xlsx/sc249_みるくＢ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc249_みるくＢ：ＥＮＤ.ss.xlsx
@@ -593,7 +593,8 @@
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>This is how I blow off the day's fatigue, but aside
-from that there's also a faint sense of expectation...</t>
+from that there's also a faint sense of
+expectation...</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -776,8 +777,8 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan dodged the question and gave her shoulders a
-little shake.</t>
+          <t>Miru-chan dodged the question and gave her shoulders
+a little shake.</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -808,7 +809,8 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>I see… You want me to be the one to start things, huh？</t>
+          <t>I see… You want me to be the one to start things,
+huh？</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1035,8 +1037,8 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan let out a low, cow-like growl, and just when
-I thought that, she puffed her cheeks out with a
+          <t>Miru-chan let out a low, cow-like growl, and just
+when I thought that, she puffed her cheeks out with a
 “puuuu” and glared at me.</t>
         </is>
       </c>
@@ -1083,8 +1085,8 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>「Then, to help you sleep, shall I give you a goodnight
-kiss？」</t>
+          <t>「Then, to help you sleep, shall I give you a
+goodnight kiss？」</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1236,8 +1238,8 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Her innocent excitement about getting a kiss warmed my
-heart as I stood up from my chair.</t>
+          <t>Her innocent excitement about getting a kiss warmed
+my heart as I stood up from my chair.</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1510,8 +1512,8 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>From Miru-chan's point of view, it must have felt like
-mine face suddenly came close.</t>
+          <t>From Miru-chan's point of view, it must have felt
+like mine face suddenly came close.</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1586,8 +1588,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>「Heyaa！ Onii-chan, saying something like that all of a
-sudden is cheating...！」</t>
+          <t>「Heyaa！ Onii-chan, saying something like that all of
+a sudden is cheating...！」</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2138,8 +2140,8 @@
       <c r="B110" s="1" t="inlineStr">
         <is>
           <t>When I involuntarily opened my mouth, Miru-chan let
-out an amused little throat sound and stuck her tongue
-out at me.</t>
+out an amused little throat sound and stuck her
+tongue out at me.</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2215,7 +2217,8 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>「lero, lerorero...pp, chu, chuu...ppa, lero, lero...！」</t>
+          <t>「lero, lerorero...pp, chu, chuu...ppa, lero,
+lero...！」</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2260,8 +2263,8 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>I’m completely at a loss because of Miru-chan’s tongue
-work.</t>
+          <t>I’m completely at a loss because of Miru-chan’s
+tongue work.</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -3187,7 +3190,8 @@
       <c r="B178" s="1" t="inlineStr">
         <is>
           <t>Unable to hold my excitement any longer, I grabbed
-Miru-chan's shoulders and gently pulled back a little.</t>
+Miru-chan's shoulders and gently pulled back a
+little.</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3538,8 +3542,8 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan can't hide her surprise and her eyes go
-wide.</t>
+          <t>Rurichiyo-chan can't hide her surprise and her eyes
+go wide.</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3677,8 +3681,8 @@
         <is>
           <t>Probably because we share a room, it seemed they had
 suspected something about the relationship between me
-and Miru-chan, and now I wondered what they were going
-to say...</t>
+and Miru-chan, and now I wondered what they were
+going to say...</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3980,8 +3984,8 @@
       <c r="B230" s="1" t="inlineStr">
         <is>
           <t>I wanted to play it cool and blow smoke here, but
-watching Nono-chan panic like that, it really wouldn’t
-work.</t>
+watching Nono-chan panic like that, it really
+wouldn’t work.</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4026,8 +4030,8 @@
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>This time Rurichiyo-chan suddenly panicked as if she’d
-remembered something.</t>
+          <t>This time Rurichiyo-chan suddenly panicked as if
+she’d remembered something.</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4193,8 +4197,8 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>In Rurichiyo-chan's head, would a kiss become the bond
-of marriage between a husband and wife？</t>
+          <t>In Rurichiyo-chan's head, would a kiss become the
+bond of marriage between a husband and wife？</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4210,7 +4214,8 @@
       <c r="B245" s="1" t="inlineStr">
         <is>
           <t>I think it's a naive misunderstanding born of purity,
-but being stated so bluntly still leaves me at a loss.</t>
+but being stated so bluntly still leaves me at a
+loss.</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4544,8 +4549,8 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>When our eyes met, Miru-chan offered a wry smile as if
-to say, "What should we do?"</t>
+          <t>When our eyes met, Miru-chan offered a wry smile as
+if to say, "What should we do?"</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4804,8 +4809,8 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Once we were alone, Miru-chan finally found her voice,
-but curled up clutching her head.</t>
+          <t>Once we were alone, Miru-chan finally found her
+voice, but curled up clutching her head.</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -5141,8 +5146,8 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>I gave a vague answer, then went back and reconsidered
-what I'd just been thinking.</t>
+          <t>I gave a vague answer, then went back and
+reconsidered what I'd just been thinking.</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5645,8 +5650,8 @@
       </c>
       <c r="B339" s="1" t="inlineStr">
         <is>
-          <t>She seemed to be slowly starting to feel the weight of
-my words.</t>
+          <t>She seemed to be slowly starting to feel the weight
+of my words.</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5691,8 +5696,8 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>Then, inside Miru-chan, thoughts shot straight through
-from marriage to everything that comes after.</t>
+          <t>Then, inside Miru-chan, thoughts shot straight
+through from marriage to everything that comes after.</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -5801,8 +5806,8 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>Because our visions of things were that different, she
-probably felt uneasy about the exchange of words.</t>
+          <t>Because our visions of things were that different,
+she probably felt uneasy about the exchange of words.</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -6120,8 +6125,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>It seems like there's been a little mix-up in what was
-said, but it's so innocent that it's actually
+          <t>It seems like there's been a little mix-up in what
+was said, but it's so innocent that it's actually
 heartwarming.</t>
         </is>
       </c>
@@ -6228,8 +6233,8 @@
       <c r="B377" s="1" t="inlineStr">
         <is>
           <t>Miru-chan chips in brightly like she always does, but
-then suddenly her eyes widen as if she just thought of
-something.</t>
+then suddenly her eyes widen as if she just thought
+of something.</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6591,8 +6596,8 @@
       <c r="B401" s="1" t="inlineStr">
         <is>
           <t>It had been a ticklish, playful moment in the flow of
-the conversation, but it suddenly turned sexual and my
-mind went blank…</t>
+the conversation, but it suddenly turned sexual and
+my mind went blank…</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -6851,8 +6856,8 @@
       </c>
       <c r="B418" s="1" t="inlineStr">
         <is>
-          <t>「Mm… Onii-chan’s penis might actually be easier to use
-and bigger than a cow’s udder？」</t>
+          <t>「Mm… Onii-chan’s penis might actually be easier to
+use and bigger than a cow’s udder？」</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6974,8 +6979,8 @@
       </c>
       <c r="B426" s="1" t="inlineStr">
         <is>
-          <t>Anyway, Miru-chan's going to do it with her hands from
-now on.</t>
+          <t>Anyway, Miru-chan's going to do it with her hands
+from now on.</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -7313,8 +7318,8 @@
       </c>
       <c r="B448" s="1" t="inlineStr">
         <is>
-          <t>It was a feeling I had never experienced before, and I
-could feel the blood rushing into my penis more
+          <t>It was a feeling I had never experienced before, and
+I could feel the blood rushing into my penis more
 strongly than usual.</t>
         </is>
       </c>
@@ -7483,7 +7488,8 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... if Miru-chan does it, everything feels good,」</t>
+          <t>「Yeah... if Miru-chan does it, everything feels
+good,」</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -7574,8 +7580,8 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>With my root held between her thumb and forefinger and
-stroked downward, a groan escaped me.</t>
+          <t>With my root held between her thumb and forefinger
+and stroked downward, a groan escaped me.</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -7759,8 +7765,8 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>It was like being made to savor that pre-orgasm shiver
-with every single stroke...</t>
+          <t>It was like being made to savor that pre-orgasm
+shiver with every single stroke...</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -7850,8 +7856,8 @@
       </c>
       <c r="B483" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha！ Onii-chan, you're like a cow！ You're a milking
-guy, huh？ Ahaha！」</t>
+          <t>「Ahaha！ Onii-chan, you're like a cow！ You're a
+milking guy, huh？ Ahaha！」</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7897,7 +7903,8 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>「Ugh... this is amazing... it's literally milking...！」</t>
+          <t>「Ugh... this is amazing... it's literally
+milking...！」</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -8170,8 +8177,8 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>「Nooo—！ I won't stop squeezing until it actually comes
-out…！」</t>
+          <t>「Nooo—！ I won't stop squeezing until it actually
+comes out…！」</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8384,8 +8391,8 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan, looking so pleased, squeezes the penis over
-and over.</t>
+          <t>Miru-chan, looking so pleased, squeezes the penis
+over and over.</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8535,8 +8542,8 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>Ugh, seriously... I can't tell whether you're adorable
-or just so damned annoying...！</t>
+          <t>Ugh, seriously... I can't tell whether you're
+adorable or just so damned annoying...！</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -9270,8 +9277,8 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>「Ah… kah！ W-well, of course… it doesn't come out a lot
-like a cow…」</t>
+          <t>「Ah… kah！ W-well, of course… it doesn't come out a
+lot like a cow…」</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -9423,7 +9430,8 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>Unconvinced, Miru-chan continued to squeeze the penis.</t>
+          <t>Unconvinced, Miru-chan continued to squeeze the
+penis.</t>
         </is>
       </c>
       <c r="C586" t="n">
@@ -9592,8 +9600,8 @@
       </c>
       <c r="B597" s="1" t="inlineStr">
         <is>
-          <t>Thinking it over, I hadn't had the most sensitive spot
-touched.</t>
+          <t>Thinking it over, I hadn't had the most sensitive
+spot touched.</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -9625,7 +9633,8 @@
       <c r="B599" s="1" t="inlineStr">
         <is>
           <t>I know that, but after being teased so much and made
-to come, I couldn't stop craving that shivery rush...！</t>
+to come, I couldn't stop craving that shivery
+rush...！</t>
         </is>
       </c>
       <c r="C599" t="n">
@@ -9731,9 +9740,9 @@
       </c>
       <c r="B606" s="1" t="inlineStr">
         <is>
-          <t>With the same hand motion and squeezing all the way to
-the tip, the skin of the penis stretched and tried to
-hide the tip.</t>
+          <t>With the same hand motion and squeezing all the way
+to the tip, the skin of the penis stretched and tried
+to hide the tip.</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -9748,8 +9757,8 @@
       </c>
       <c r="B607" s="1" t="inlineStr">
         <is>
-          <t>...It's not what I expected, but this helps in its own
-way.</t>
+          <t>...It's not what I expected, but this helps in its
+own way.</t>
         </is>
       </c>
       <c r="C607" t="n">
@@ -9949,8 +9958,8 @@
       <c r="B620" s="1" t="inlineStr">
         <is>
           <t>As I thought... it was fine when it was just the
-shaft, but getting squeezed the same way at the tip is
-unbearable.</t>
+shaft, but getting squeezed the same way at the tip
+is unbearable.</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -10286,8 +10295,8 @@
       <c r="B642" s="1" t="inlineStr">
         <is>
           <t>…Miru-chan probably thinks she’s doing the right
-thing, but for me it’s getting to the point where it’s
-no longer a joke.</t>
+thing, but for me it’s getting to the point where
+it’s no longer a joke.</t>
         </is>
       </c>
       <c r="C642" t="n">
@@ -10349,8 +10358,8 @@
       </c>
       <c r="B646" s="1" t="inlineStr">
         <is>
-          <t>「Nn...？ You're twitching again, huh？ See, you're going
-to come a little more, aren't you？」</t>
+          <t>「Nn...？ You're twitching again, huh？ See, you're
+going to come a little more, aren't you？」</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -10380,8 +10389,8 @@
       </c>
       <c r="B648" s="1" t="inlineStr">
         <is>
-          <t>With each stroke, a pleasurable electric current races
-through my whole body…！</t>
+          <t>With each stroke, a pleasurable electric current
+races through my whole body…！</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10881,8 +10890,8 @@
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan panics and worries over me, but I don’t have
-the luxury to put on a brave face at all.</t>
+          <t>Miru-chan panics and worries over me, but I don’t
+have the luxury to put on a brave face at all.</t>
         </is>
       </c>
       <c r="C681" t="n">
@@ -10973,9 +10982,9 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>And then, trapped by a pleasure I’d never felt before,
-I lost consciousness as if sinking to the bottom of
-the sea….</t>
+          <t>And then, trapped by a pleasure I’d never felt
+before, I lost consciousness as if sinking to the
+bottom of the sea….</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -11373,9 +11382,9 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>…When we went to greet her parents, Miru-chan, without
-a shred of embarrassment, said she was going to marry
-Onii-chan, so I totally freaked out.</t>
+          <t>…When we went to greet her parents, Miru-chan,
+without a shred of embarrassment, said she was going
+to marry Onii-chan, so I totally freaked out.</t>
         </is>
       </c>
       <c r="C713" t="n">
@@ -11608,8 +11617,8 @@
       </c>
       <c r="B728" s="1" t="inlineStr">
         <is>
-          <t>Well, it's exactly true in spirit, but socially it's a
-little different…</t>
+          <t>Well, it's exactly true in spirit, but socially it's
+a little different…</t>
         </is>
       </c>
       <c r="C728" t="n">
@@ -11805,8 +11814,8 @@
       </c>
       <c r="B741" s="1" t="inlineStr">
         <is>
-          <t>……When I look at Miru-chan's smile, my heart naturally
-grows warm.</t>
+          <t>……When I look at Miru-chan's smile, my heart
+naturally grows warm.</t>
         </is>
       </c>
       <c r="C741" t="n">
@@ -11867,8 +11876,8 @@
       <c r="B745" s="1" t="inlineStr">
         <is>
           <t>「Ah… well, I was just thinking that being able to be
-with Miru-chan like this, I'd be happy for the rest of
-my life…」</t>
+with Miru-chan like this, I'd be happy for the rest
+of my life…」</t>
         </is>
       </c>
       <c r="C745" t="n">

--- a/processed_ruby_restored_xlsx/sc249_みるくＢ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc249_みるくＢ：ＥＮＤ.ss.xlsx
@@ -900,7 +900,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>「Is that so？ Hehe...！」</t>
+          <t>Is that so？ Hehe...！</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1513,7 +1513,7 @@
       <c r="B69" s="1" t="inlineStr">
         <is>
           <t>From Miru-chan's point of view, it must have felt
-like mine face suddenly came close.</t>
+like his face suddenly came close.</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh... sorry, sorry」</t>
+          <t>Heh heh... sorry, sorry</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>「Nn, chu-chu！ Chu, f... fuu... chu, chu, pu, chu！」</t>
+          <t>Nn, chu-chu！ Chu, f... fuu... chu, chu, pu, chu！</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2123,8 +2123,8 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>「Mmm~？ Hah, pff… lero... lero, reru... retchu, chu,
-chupuu...」</t>
+          <t>Mmm~？ Hah, pff… lero... lero, reru... retchu, chu,
+chupuu...</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>「Nnfa... ah, afu, faa, faaa...」</t>
+          <t>Nnfa... ah, afu, faa, faaa...</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3018,9 +3018,9 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>It was as if she were greedily devouring pleasure on
-pure instinct, craving the slick sensation of our
-tongues rubbing together...</t>
+          <t>It was like she was devouring pleasure on instinct,
+seeking the刺激 of her tongue's mucous membrane meeting
+mine...</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3282,7 +3282,7 @@
       <c r="B184" s="1" t="inlineStr">
         <is>
           <t>Before I knew it, everyone had come into the living
-room and were peeking at us from behind the door...</t>
+room and were peeking at us from behind the door..."</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>「Y-... Janitor-sensei！ Wh-what is going on here?！」</t>
+          <t>Y-... Janitor-sensei！ Wh-what is going on here?！</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -4198,7 +4198,7 @@
       <c r="B244" s="1" t="inlineStr">
         <is>
           <t>In Rurichiyo-chan's head, would a kiss become the
-bond of marriage between a husband and wife？</t>
+bond of marriage between a husband and wife？"</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>And then I nodded to myself.</t>
+          <t>And then he nodded to himself.</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5807,7 +5807,8 @@
       <c r="B349" s="1" t="inlineStr">
         <is>
           <t>Because our visions of things were that different,
-she probably felt uneasy about the exchange of words.</t>
+they probably felt uneasy about the exchange of
+words.</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -5913,7 +5914,7 @@
       </c>
       <c r="B356" s="1" t="inlineStr">
         <is>
-          <t>「What？! I'm not my groom!？」</t>
+          <t>What？! He's not my groom!？</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -7088,7 +7089,7 @@
       </c>
       <c r="B433" s="1" t="inlineStr">
         <is>
-          <t>「H‑hooo…！」</t>
+          <t>H‑hooo…！</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -8072,7 +8073,7 @@
       <c r="B497" s="1" t="inlineStr">
         <is>
           <t>Ahhh... each time Miru-chan's fingers squeeze me, it
-feels like my whole penis is being taken away...</t>
+feels like my whole penis is being taken away..."</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8102,7 +8103,7 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>「Nnhf... nnh~... nnhfuh~！」</t>
+          <t>Nnhf... nnh~... nnhfuh~！</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8177,8 +8178,8 @@
       </c>
       <c r="B504" s="1" t="inlineStr">
         <is>
-          <t>「Nooo—！ I won't stop squeezing until it actually
-comes out…！」</t>
+          <t>Nooo—！ I won」t stop squeezing until it actually comes
+out…！</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -8208,7 +8209,7 @@
       </c>
       <c r="B506" s="1" t="inlineStr">
         <is>
-          <t>「O-ohh...！？」</t>
+          <t>O-ohh...！？</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8224,7 +8225,7 @@
       <c r="B507" s="1" t="inlineStr">
         <is>
           <t>Miru-chan said, sounding oddly cheerful, as she kept
-on squeezing my penis.</t>
+on squeezing his penis.</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8270,7 +8271,7 @@
       </c>
       <c r="B510" s="1" t="inlineStr">
         <is>
-          <t>「Mi‑ Miru-chan... it feels too good, so...！」</t>
+          <t>Mi‑ Miru-chan... it feels too good, so...！</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -8482,7 +8483,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah... it feels so good...！」</t>
+          <t>Y-yeah... it feels so good...！</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8512,7 +8513,7 @@
       </c>
       <c r="B526" s="1" t="inlineStr">
         <is>
-          <t>「Is that so... nfu！ Nfufu...！」</t>
+          <t>Is that so... nfu！ Nfufu...！</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -8573,8 +8574,8 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>「Okaaay, so let's do a 'byuu-byuu,' okay？ Nfu！
-Nfufu...！」</t>
+          <t>Okaaay, so let's do a 'byuu-byuu,' okay？ Nfu！
+Nfufu...！</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8863,8 +8864,8 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>When I couldn't hold back and came, Miru-chan let out
-a delighted sound and kept insisting.</t>
+          <t>When he couldn't hold back and came, Miru-chan let
+out a delighted sound and kept insisting.</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -8971,7 +8972,7 @@
       </c>
       <c r="B556" s="1" t="inlineStr">
         <is>
-          <t>Even though semen is coming out, I still keep
+          <t>Even though semen is coming out, he still keeps
 rhythmically squeezing the penis.</t>
         </is>
       </c>
@@ -9523,7 +9524,7 @@
       </c>
       <c r="B592" s="1" t="inlineStr">
         <is>
-          <t>A-again... I'm going to come...！？</t>
+          <t>A-again... I'm going to come...！？"</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -10480,7 +10481,7 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>「Mi-Miru-cha…」</t>
+          <t>Mi-Miru-cha…</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10800,7 +10801,7 @@
       </c>
       <c r="B675" s="1" t="inlineStr">
         <is>
-          <t>I'm a guy, and yet... squirting... .</t>
+          <t>He's a guy, and yet... squirting... .</t>
         </is>
       </c>
       <c r="C675" t="n">
